--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487888_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487888_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5857</v>
+        <v>3.2771</v>
       </c>
       <c r="E2" t="n">
-        <v>1.297</v>
+        <v>2.0471</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2887</v>
+        <v>1.23</v>
       </c>
       <c r="G2" t="n">
         <v>2.19</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4149</v>
+        <v>0.2765</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7829</v>
+        <v>-0.0328</v>
       </c>
       <c r="U2" t="n">
-        <v>0.368</v>
+        <v>0.3093</v>
       </c>
       <c r="V2" t="n">
         <v>-0.23</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4309</v>
+        <v>2.8992</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2199</v>
+        <v>3.5414</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.789</v>
+        <v>-0.6422</v>
       </c>
       <c r="G3" t="n">
         <v>2.2988</v>
@@ -688,13 +688,13 @@
         <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.4868</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8482</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.107</v>
+        <v>0.0398</v>
       </c>
       <c r="V3" t="n">
         <v>0.2547</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.119</v>
+        <v>1.6725</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9271</v>
+        <v>3.5373</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8081</v>
+        <v>-1.8648</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.0377</v>
+        <v>0.0595</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5332</v>
+        <v>-0.872</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4956</v>
+        <v>0.9315</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0362</v>
+        <v>1.9987</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7084</v>
+        <v>0.2834</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7446</v>
+        <v>1.7153</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0738</v>
+        <v>-1.9392</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8248</v>
+        <v>-1.1554</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.249</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0081</v>
+        <v>0.281</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5559</v>
+        <v>0.371</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4522</v>
+        <v>-0.09</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.7076</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3351</v>
+        <v>1.1675</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6027</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0908</v>
+        <v>1.2221</v>
       </c>
       <c r="E5" t="n">
-        <v>4.073</v>
+        <v>3.1771</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9822</v>
+        <v>-1.9549</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0595</v>
+        <v>-1.0377</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.872</v>
+        <v>-1.5332</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9315</v>
+        <v>0.4956</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9987</v>
+        <v>0.0362</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2834</v>
+        <v>-0.7084</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7153</v>
+        <v>0.7446</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9392</v>
+        <v>-1.0738</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1554</v>
+        <v>-0.8248</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.249</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6993</v>
+        <v>1.1112</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.8058</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2075</v>
+        <v>0.3054</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7076</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1675</v>
+        <v>2.3351</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4599</v>
+        <v>-1.6027</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2162</v>
+        <v>0.8526</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1693</v>
+        <v>2.2654</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3856</v>
+        <v>-1.4128</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3189</v>
+        <v>1.8446</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7336</v>
+        <v>-0.3752</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5854</v>
+        <v>2.2198</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9804</v>
+        <v>2.5264</v>
       </c>
       <c r="K6" t="n">
-        <v>0.648</v>
+        <v>0.0576</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3324</v>
+        <v>2.4689</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6614</v>
+        <v>-0.6818</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0856</v>
+        <v>-0.4328</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.747</v>
+        <v>-0.249</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4568</v>
+        <v>0.2081</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2115</v>
+        <v>-0.0326</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.261</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2801</v>
+        <v>0.2284</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6899</v>
+        <v>-1.1675</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6899</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9113</v>
+        <v>0.5219</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2654</v>
+        <v>-0.2765</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3541</v>
+        <v>0.7984</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8446</v>
+        <v>1.3189</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3752</v>
+        <v>0.7336</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2198</v>
+        <v>0.5854</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5264</v>
+        <v>1.9804</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0576</v>
+        <v>0.648</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4689</v>
+        <v>1.3324</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6818</v>
+        <v>-0.6614</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4328</v>
+        <v>0.0856</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.249</v>
+        <v>-0.747</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2081</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2081</v>
+        <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0261</v>
+        <v>0.5172</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.261</v>
+        <v>-0.1757</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2871</v>
+        <v>0.6929</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1675</v>
+        <v>-0.6899</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1173</v>
+        <v>0.449</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-0.7529</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0845</v>
+        <v>1.2019</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1473</v>
@@ -1078,13 +1078,13 @@
         <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3379</v>
+        <v>-0.0062</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4567</v>
+        <v>-0.2424</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1188</v>
+        <v>0.2362</v>
       </c>
       <c r="V8" t="n">
         <v>-0.23</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0287</v>
+        <v>-0.0873</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9647</v>
+        <v>-1.2862</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9933999999999999</v>
+        <v>1.1989</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0711</v>
@@ -1156,13 +1156,13 @@
         <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6804</v>
+        <v>0.5645</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6458</v>
+        <v>0.3244</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0346</v>
+        <v>0.2401</v>
       </c>
       <c r="V9" t="n">
         <v>0.4599</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5832</v>
+        <v>-2.2808</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3343</v>
+        <v>-0.12</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2489</v>
+        <v>-2.1608</v>
       </c>
       <c r="G10" t="n">
         <v>0.1438</v>
@@ -1234,13 +1234,13 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.398</v>
+        <v>-0.0956</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3948</v>
+        <v>-0.1804</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0032</v>
+        <v>0.0849</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4966</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. AIZPITARTE ARANZA</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8143</v>
+        <v>-2.7033</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8648</v>
+        <v>-0.5245</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9495</v>
+        <v>-2.1788</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6458</v>
+        <v>-2.7292</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6633</v>
+        <v>0.405</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.3091</v>
+        <v>-3.1343</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.3272</v>
+        <v>-0.3776</v>
       </c>
       <c r="K11" t="n">
-        <v>0.341</v>
+        <v>1.6178</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.6682</v>
+        <v>-1.9954</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3186</v>
+        <v>-2.3516</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3223</v>
+        <v>-1.2127</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6409</v>
+        <v>-1.1389</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4568</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1012</v>
+        <v>0.4798</v>
       </c>
       <c r="T11" t="n">
-        <v>1.295</v>
+        <v>0.1829</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1937</v>
+        <v>0.2969</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7265</v>
+        <v>0.3786</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1675</v>
+        <v>1.7513</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8941</v>
+        <v>-1.3727</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>I. AIZPITARTE ARANZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1701</v>
+        <v>-2.8906</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1675</v>
+        <v>-1.2934</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0026</v>
+        <v>-1.5972</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7292</v>
+        <v>-3.6458</v>
       </c>
       <c r="H12" t="n">
-        <v>0.405</v>
+        <v>0.6633</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.1343</v>
+        <v>-4.3091</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3776</v>
+        <v>-3.3272</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6178</v>
+        <v>0.341</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9954</v>
+        <v>-3.6682</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3516</v>
+        <v>-0.3186</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2127</v>
+        <v>0.3223</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1389</v>
+        <v>-0.6409</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S12" t="n">
-        <v>0.013</v>
+        <v>1.0249</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.46</v>
+        <v>0.8663</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4731</v>
+        <v>0.1586</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3786</v>
+        <v>-1.7265</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7513</v>
+        <v>1.1675</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.3727</v>
+        <v>-2.8941</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.932300000000003</v>
+        <v>2.932399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>10.3146</v>
+        <v>10.3148</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.3822</v>
+        <v>-7.3823</v>
       </c>
       <c r="G13" t="n">
         <v>0.224499999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>5.2458</v>
+        <v>5.245800000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-5.021100000000001</v>
@@ -1444,7 +1444,7 @@
         <v>10.1667</v>
       </c>
       <c r="K13" t="n">
-        <v>9.677199999999999</v>
+        <v>9.677200000000001</v>
       </c>
       <c r="L13" t="n">
         <v>0.4895999999999998</v>
@@ -1456,7 +1456,7 @@
         <v>-4.4312</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.510899999999999</v>
+        <v>-5.5109</v>
       </c>
       <c r="P13" t="n">
         <v>2.0811</v>
@@ -1468,7 +1468,7 @@
         <v>10.4059</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6337</v>
+        <v>3.6339</v>
       </c>
       <c r="T13" t="n">
         <v>1.1314</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7574</v>
+        <v>4.1398</v>
       </c>
       <c r="E14" t="n">
-        <v>7.0182</v>
+        <v>5.518</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2607</v>
+        <v>-1.3782</v>
       </c>
       <c r="G14" t="n">
         <v>1.2077</v>
@@ -1546,13 +1546,13 @@
         <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4562</v>
+        <v>-0.1615</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6179</v>
+        <v>0.1177</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1617</v>
+        <v>-0.2791</v>
       </c>
       <c r="V14" t="n">
         <v>4.7585</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2451</v>
+        <v>2.7944</v>
       </c>
       <c r="E15" t="n">
-        <v>5.723</v>
+        <v>5.8302</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.478</v>
+        <v>-3.0358</v>
       </c>
       <c r="G15" t="n">
         <v>3.085</v>
@@ -1624,13 +1624,13 @@
         <v>1.4568</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1324</v>
+        <v>-0.5831</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.5486</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5233</v>
+        <v>-0.0345</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1238</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0417</v>
+        <v>-0.0567</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4767</v>
+        <v>0.5838</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.435</v>
+        <v>-0.6405</v>
       </c>
       <c r="G16" t="n">
         <v>0.3372</v>
@@ -1702,13 +1702,13 @@
         <v>0.4162</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2518</v>
+        <v>-0.3502</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5219</v>
+        <v>-0.4148</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2701</v>
+        <v>0.0646</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4599</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. LARA CALDERA</t>
+          <t>A. MAZAIRA GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5881</v>
+        <v>-0.3401</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1374</v>
+        <v>1.1196</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4508</v>
+        <v>-1.4597</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2886</v>
+        <v>0.4043</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0788</v>
+        <v>-1.2898</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2098</v>
+        <v>1.6941</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0584</v>
+        <v>1.9355</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0192</v>
+        <v>0.3558</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0392</v>
+        <v>1.5798</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.347</v>
+        <v>-1.5312</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.098</v>
+        <v>-1.6455</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.249</v>
+        <v>0.1143</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2995</v>
+        <v>-0.5769</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1957</v>
+        <v>-0.359</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1037</v>
+        <v>-0.2178</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MAZAIRA GOMEZ</t>
+          <t>D. LARA CALDERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1195</v>
+        <v>-0.5294</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3696</v>
+        <v>-0.1374</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4891</v>
+        <v>-0.392</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4043</v>
+        <v>-0.2886</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2898</v>
+        <v>-0.0788</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6941</v>
+        <v>-0.2098</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9355</v>
+        <v>0.0584</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3558</v>
+        <v>0.0192</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5798</v>
+        <v>0.0392</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5312</v>
+        <v>-0.347</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6455</v>
+        <v>-0.098</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1143</v>
+        <v>-0.249</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4568</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3563</v>
+        <v>-0.2407</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1091</v>
+        <v>-0.1957</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2472</v>
+        <v>-0.045</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0852</v>
+        <v>-1.2471</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1005</v>
+        <v>0.8506</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1857</v>
+        <v>-2.0976</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9139</v>
@@ -1936,13 +1936,13 @@
         <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3576</v>
+        <v>-0.5195</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1091</v>
+        <v>-0.359</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2485</v>
+        <v>-0.1604</v>
       </c>
       <c r="V19" t="n">
         <v>-0.23</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. UNIACKE</t>
+          <t>L. PAUL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4791</v>
+        <v>-2.2797</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9776</v>
+        <v>-1.0785</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-1.2011</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0354</v>
+        <v>-1.0491</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8231</v>
+        <v>-1.6826</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2123</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3904</v>
+        <v>0.4574</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3904</v>
+        <v>-0.67</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.1275</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.645</v>
+        <v>-1.5065</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4328</v>
+        <v>-1.0126</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2123</v>
+        <v>-0.4939</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.8325</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3888</v>
+        <v>-0.2337</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4534</v>
+        <v>0.0853</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0646</v>
+        <v>-0.319</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. PAUL</t>
+          <t>A. PALAZUELOS PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4955</v>
+        <v>-2.6234</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9714</v>
+        <v>-2.8977</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5241</v>
+        <v>0.2743</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0491</v>
+        <v>-0.9718</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6826</v>
+        <v>-1.2363</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.2645</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4574</v>
+        <v>-1.0042</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.67</v>
+        <v>-0.4074</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1275</v>
+        <v>-0.5968</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5065</v>
+        <v>0.0324</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0126</v>
+        <v>-0.829</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4939</v>
+        <v>0.8613</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.4568</v>
+        <v>0.2081</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4495</v>
+        <v>-1.046</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1924</v>
+        <v>-0.8529</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6419</v>
+        <v>-0.193</v>
       </c>
       <c r="V21" t="n">
-        <v>0.4599</v>
+        <v>-0.8137</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. PALAZUELOS PEREZ</t>
+          <t>P. UNIACKE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2091</v>
+        <v>-2.7902</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2191</v>
+        <v>-2.4062</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0101</v>
+        <v>-0.3841</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9718</v>
+        <v>-2.0354</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2363</v>
+        <v>-1.8231</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2645</v>
+        <v>-0.2123</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0042</v>
+        <v>-1.3904</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4074</v>
+        <v>-1.3904</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5968</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0324</v>
+        <v>-0.645</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.829</v>
+        <v>-0.4328</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8613</v>
+        <v>-0.2123</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2081</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6317</v>
+        <v>0.0776</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1744</v>
+        <v>0.0248</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4573</v>
+        <v>0.0529</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8137</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9323</v>
+        <v>-2.9324</v>
       </c>
       <c r="E23" t="n">
-        <v>7.382499999999999</v>
+        <v>7.382399999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-10.3148</v>
+        <v>-10.3147</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2245999999999997</v>
+        <v>-0.2246000000000001</v>
       </c>
       <c r="H23" t="n">
         <v>-5.2457</v>
       </c>
       <c r="I23" t="n">
-        <v>5.021100000000001</v>
+        <v>5.0211</v>
       </c>
       <c r="J23" t="n">
         <v>9.9421</v>
@@ -2227,7 +2227,7 @@
         <v>4.4314</v>
       </c>
       <c r="L23" t="n">
-        <v>5.510899999999999</v>
+        <v>5.5109</v>
       </c>
       <c r="M23" t="n">
         <v>-10.1667</v>
@@ -2236,7 +2236,7 @@
         <v>-9.677099999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4897999999999998</v>
+        <v>-0.4898000000000001</v>
       </c>
       <c r="P23" t="n">
         <v>-2.0813</v>
@@ -2248,13 +2248,13 @@
         <v>8.3246</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.6338</v>
+        <v>-3.634</v>
       </c>
       <c r="T23" t="n">
         <v>-2.5022</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1315</v>
+        <v>-1.1313</v>
       </c>
       <c r="V23" t="n">
         <v>3.0072</v>
